--- a/forms/trg/Formulir_TRG_ffoodtech.xlsx
+++ b/forms/trg/Formulir_TRG_ffoodtech.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B42)</f>
+        <f>COUNTA(Anggota!B5:B44)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F42)</f>
+        <f>COUNTA(Anggota!F5:F44)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,12 +925,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Muhpidah, STP, M.Si</t>
+          <t>Prof. Dr. Ir. Meta Mahendradatta</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -940,16 +940,28 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Agroindustrial Process Technology</t>
+          <t>Food Quality Control and Monitoring</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0516-8411</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>5980684</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>14626764200</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -962,12 +974,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Andi Rahmayanti R., S.TP., M.Si</t>
+          <t>Muhpidah, STP, M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,28 +989,16 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Food Biochemistry</t>
+          <t>Agroindustrial Process Technology</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0009-0007-3608-0945</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6699933</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57202442953</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Arfina Sukmawati Arifin, S.TP., M.Si</t>
+          <t>Andi Rahmayanti R., S.TP., M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1026,22 +1026,26 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Food Chemistry and Microbiology</t>
+          <t>Food Biochemistry</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0009-0007-3608-0945</t>
+        </is>
+      </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6779551</t>
+          <t>6699933</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>58336384200</t>
+          <t>57202442953</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1056,12 +1060,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Asfar, S.TP., M.Si</t>
+          <t>Arfina Sukmawati Arifin, S.TP., M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1071,26 +1075,22 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Food Analysis and Processing</t>
+          <t>Food Chemistry and Microbiology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-0495-5838</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6048316</t>
+          <t>6779551</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>57200989241</t>
+          <t>58336384200</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Februadi Bastian, S.TP., M.Si</t>
+          <t>Dr. Muhammad Asfar, S.TP., M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Food Chemistry</t>
+          <t>Food Analysis and Processing</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1129,7 +1129,7 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4198-4662</t>
+          <t>0000-0002-0495-5838</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57202431233</t>
+          <t>57200989241</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr.rer.nat. Zainal, S.TP., M.FoodTech</t>
+          <t>Dr. Februadi Bastian, S.TP., M.Si</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Food Quality Control and Monitoring</t>
+          <t>Food Chemistry</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1178,17 +1178,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9638-0711</t>
+          <t>0000-0002-4198-4662</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>5981356</t>
+          <t>6048316</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57216221263</t>
+          <t>57202431233</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Takao Nagano, Ph.D</t>
+          <t>Dr.rer.nat. Zainal, S.TP., M.FoodTech</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Ishikawa Prefectural University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Food Chemistry</t>
+          <t>Food Quality Control and Monitoring</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1227,13 +1227,17 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6105-8703</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="n"/>
+          <t>0000-0001-9638-0711</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>5981356</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>7202185997</t>
+          <t>57216221263</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1248,33 +1252,37 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ing. Knut Franke</t>
+          <t>Prof. Takao Nagano, Ph.D</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Leibniz Universität Hannover</t>
+          <t>Ishikawa Prefectural University</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Food Processing and Engineering</t>
+          <t>Food Chemistry</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-6105-8703</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>7101956926</t>
+          <t>7202185997</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1289,23 +1297,35 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Andi Nur Fajri Suloi, S.TP., M.TP</t>
+          <t>Dr. Ing. Knut Franke</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Leibniz Universität Hannover</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Food Processing and Engineering</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>7101956926</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1318,12 +1338,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Nur Amaliah, S.TP., M.Si</t>
+          <t>Andi Nur Fajri Suloi, S.TP., M.TP</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1347,12 +1367,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Siti Aisa Liputo, S.Si., M.Si</t>
+          <t>Nur Amaliah, S.TP., M.Si</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1376,12 +1396,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Dwi Ghina Nadhifa, S.TP</t>
+          <t>Siti Aisa Liputo, S.Si., M.Si</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1390,17 +1410,9 @@
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>0009-0000-4213-0901</t>
-        </is>
-      </c>
+      <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>59141939500</t>
-        </is>
-      </c>
+      <c r="L16" s="12" t="n"/>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1413,31 +1425,31 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Muhpidah, STP, M.Si</t>
+          <t>Dwi Ghina Nadhifa, S.TP</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Agroindustrial Process Technology</t>
-        </is>
-      </c>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>0009-0000-4213-0901</t>
+        </is>
+      </c>
       <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>59141939500</t>
+        </is>
+      </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1450,12 +1462,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Andi Rahmayanti R., S.TP., M.Si</t>
+          <t>Prof. Dr. Ir. Meta Mahendradatta</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1465,7 +1477,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Food Biochemistry</t>
+          <t>Food Quality Control and Monitoring</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1474,17 +1486,17 @@
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>0009-0007-3608-0945</t>
+          <t>0000-0003-0516-8411</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
         <is>
-          <t>6699933</t>
+          <t>5980684</t>
         </is>
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>57202442953</t>
+          <t>14626764200</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
@@ -1499,12 +1511,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Arfina Sukmawati Arifin, S.TP., M.Si</t>
+          <t>Muhpidah, STP, M.Si</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1514,7 +1526,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Food Chemistry and Microbiology</t>
+          <t>Agroindustrial Process Technology</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1522,16 +1534,8 @@
       <c r="H19" s="12" t="n"/>
       <c r="I19" s="12" t="n"/>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>6779551</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>58336384200</t>
-        </is>
-      </c>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1544,12 +1548,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Asfar, S.TP., M.Si</t>
+          <t>Andi Rahmayanti R., S.TP., M.Si</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1559,7 +1563,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Food Analysis and Processing</t>
+          <t>Food Biochemistry</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1568,17 +1572,17 @@
       <c r="I20" s="12" t="n"/>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0495-5838</t>
+          <t>0009-0007-3608-0945</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>6048316</t>
+          <t>6699933</t>
         </is>
       </c>
       <c r="L20" s="11" t="inlineStr">
         <is>
-          <t>57200989241</t>
+          <t>57202442953</t>
         </is>
       </c>
       <c r="M20" s="11" t="inlineStr">
@@ -1593,12 +1597,12 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Dr. Februadi Bastian, S.TP., M.Si</t>
+          <t>Arfina Sukmawati Arifin, S.TP., M.Si</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1608,26 +1612,22 @@
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Food Chemistry</t>
+          <t>Food Chemistry and Microbiology</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="n"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-4198-4662</t>
-        </is>
-      </c>
+      <c r="J21" s="12" t="n"/>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>6048316</t>
+          <t>6779551</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>57202431233</t>
+          <t>58336384200</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Dr.rer.nat. Zainal, S.TP., M.FoodTech</t>
+          <t>Dr. Muhammad Asfar, S.TP., M.Si</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Food Quality Control and Monitoring</t>
+          <t>Food Analysis and Processing</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1666,17 +1666,17 @@
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9638-0711</t>
+          <t>0000-0002-0495-5838</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>5981356</t>
+          <t>6048316</t>
         </is>
       </c>
       <c r="L22" s="11" t="inlineStr">
         <is>
-          <t>57216221263</t>
+          <t>57200989241</t>
         </is>
       </c>
       <c r="M22" s="11" t="inlineStr">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Prof. Takao Nagano, Ph.D</t>
+          <t>Dr. Februadi Bastian, S.TP., M.Si</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Ishikawa Prefectural University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -1715,13 +1715,17 @@
       <c r="I23" s="12" t="n"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6105-8703</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="n"/>
+          <t>0000-0002-4198-4662</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
+        <is>
+          <t>6048316</t>
+        </is>
+      </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>7202185997</t>
+          <t>57202431233</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
@@ -1736,33 +1740,41 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ing. Knut Franke</t>
+          <t>Dr.rer.nat. Zainal, S.TP., M.FoodTech</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Leibniz Universität Hannover</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Food Processing and Engineering</t>
+          <t>Food Quality Control and Monitoring</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-9638-0711</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
+        <is>
+          <t>5981356</t>
+        </is>
+      </c>
       <c r="L24" s="11" t="inlineStr">
         <is>
-          <t>7101956926</t>
+          <t>57216221263</t>
         </is>
       </c>
       <c r="M24" s="11" t="inlineStr">
@@ -1777,23 +1789,39 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Andi Nur Fajri Suloi, S.TP., M.TP</t>
+          <t>Prof. Takao Nagano, Ph.D</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Ishikawa Prefectural University</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Food Chemistry</t>
+        </is>
+      </c>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12" t="n"/>
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
+      <c r="J25" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-6105-8703</t>
+        </is>
+      </c>
       <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>7202185997</t>
+        </is>
+      </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1806,23 +1834,35 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Nur Amaliah, S.TP., M.Si</t>
+          <t>Dr. Ing. Knut Franke</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Leibniz Universität Hannover</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Food Processing and Engineering</t>
+        </is>
+      </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
       <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>7101956926</t>
+        </is>
+      </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1835,12 +1875,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Siti Aisa Liputo, S.Si., M.Si</t>
+          <t>Andi Nur Fajri Suloi, S.TP., M.TP</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D27" s="12" t="n"/>
@@ -1864,12 +1904,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Dwi Ghina Nadhifa, S.TP</t>
+          <t>Nur Amaliah, S.TP., M.Si</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D28" s="12" t="n"/>
@@ -1878,17 +1918,9 @@
       <c r="G28" s="12" t="n"/>
       <c r="H28" s="12" t="n"/>
       <c r="I28" s="12" t="n"/>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>0009-0000-4213-0901</t>
-        </is>
-      </c>
+      <c r="J28" s="12" t="n"/>
       <c r="K28" s="12" t="n"/>
-      <c r="L28" s="11" t="inlineStr">
-        <is>
-          <t>59141939500</t>
-        </is>
-      </c>
+      <c r="L28" s="12" t="n"/>
       <c r="M28" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1901,43 +1933,23 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir Abu Bakar Tawali</t>
+          <t>Siti Aisa Liputo, S.Si., M.Si</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Food Technology and Analysis</t>
-        </is>
-      </c>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="12" t="n"/>
       <c r="H29" s="12" t="n"/>
       <c r="I29" s="12" t="n"/>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-0196-8497</t>
-        </is>
-      </c>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>5981356</t>
-        </is>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>6506657332</t>
-        </is>
-      </c>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
       <c r="M29" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1950,41 +1962,29 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir Abu Bakar Tawali</t>
+          <t>Dwi Ghina Nadhifa, S.TP</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>Food Technology and Analysis</t>
-        </is>
-      </c>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="12" t="n"/>
       <c r="H30" s="12" t="n"/>
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-0196-8497</t>
-        </is>
-      </c>
-      <c r="K30" s="11" t="inlineStr">
-        <is>
-          <t>5981356</t>
-        </is>
-      </c>
+          <t>0009-0000-4213-0901</t>
+        </is>
+      </c>
+      <c r="K30" s="12" t="n"/>
       <c r="L30" s="11" t="inlineStr">
         <is>
-          <t>6506657332</t>
+          <t>59141939500</t>
         </is>
       </c>
       <c r="M30" s="11" t="inlineStr">
@@ -1997,35 +1997,99 @@
       <c r="A31" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="11" t="n"/>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Ir Abu Bakar Tawali</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Food Technology and Analysis</t>
+        </is>
+      </c>
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="12" t="n"/>
       <c r="H31" s="12" t="n"/>
       <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="12" t="n"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0196-8497</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr">
+        <is>
+          <t>5981356</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>6506657332</t>
+        </is>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="11" t="n"/>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Ir Abu Bakar Tawali</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Food Technology and Analysis</t>
+        </is>
+      </c>
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="12" t="n"/>
       <c r="H32" s="12" t="n"/>
       <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0196-8497</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
+        <is>
+          <t>5981356</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>6506657332</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -2197,15 +2261,49 @@
       <c r="L42" s="12" t="n"/>
       <c r="M42" s="12" t="n"/>
     </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="12" t="n"/>
+      <c r="D43" s="12" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="12" t="n"/>
+      <c r="L43" s="12" t="n"/>
+      <c r="M43" s="12" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="12" t="n"/>
+      <c r="D44" s="12" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="12" t="n"/>
+      <c r="H44" s="12" t="n"/>
+      <c r="I44" s="12" t="n"/>
+      <c r="J44" s="12" t="n"/>
+      <c r="K44" s="12" t="n"/>
+      <c r="L44" s="12" t="n"/>
+      <c r="M44" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
